--- a/SuppXLS/Scen_ELC_CO2_BOUND.xlsx
+++ b/SuppXLS/Scen_ELC_CO2_BOUND.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22CEEAF9-52A7-4FBF-92B7-720E01DAB284}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7231BEC-5A3C-4960-9EAA-01BC88A07C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ELCCO2_BND" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,13 +33,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
     <author>Gary Goldstein</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="1" shapeId="0">
+    <comment ref="I2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -61,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="1" shapeId="0">
+    <comment ref="N2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
   <si>
     <t>Pset_CI</t>
   </si>
@@ -178,12 +183,45 @@
   </si>
   <si>
     <t>DemoS_010</t>
+  </si>
+  <si>
+    <t>jkl;</t>
+  </si>
+  <si>
+    <t>jk</t>
+  </si>
+  <si>
+    <t>kjl</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>kl;</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>jk;</t>
+  </si>
+  <si>
+    <t>l;j</t>
+  </si>
+  <si>
+    <t>;l</t>
+  </si>
+  <si>
+    <t>l;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -288,15 +326,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="1"/>
-    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2"/>
+    <cellStyle name="Normal 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -462,9 +500,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -502,9 +540,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -537,26 +575,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -589,26 +610,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -781,8 +785,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1506,6 +1510,68 @@
         <v>1284809.0276764501</v>
       </c>
     </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>42</v>
+      </c>
+      <c r="L37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I50" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
